--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-lagos.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M215"/>
+  <dimension ref="A1:M218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>1989.6</v>
+        <v>1979.37</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5513.5</v>
+        <v>5458.47</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1048.23</v>
+        <v>1037.25</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1653.31</v>
+        <v>1644.28</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>2816.82</v>
+        <v>2801.43</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>821.59</v>
+        <v>817.09</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>2726.02</v>
+        <v>2711.09</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2596.47</v>
+        <v>2582.25</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>849</v>
+        <v>844.35</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>1250.16</v>
+        <v>1263.76</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>837.3</v>
+        <v>840.05</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2734.64</v>
+        <v>2781.85</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1481.51</v>
+        <v>1507.08</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>4219.25</v>
+        <v>4292.08</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2670.41</v>
+        <v>2716.51</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>13615.56</v>
+        <v>13709.88</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>1146.6</v>
+        <v>1151.94</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>945.74</v>
+        <v>950.14</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>893.45</v>
+        <v>897.61</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1044.43</v>
+        <v>1042.82</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>4591.77</v>
+        <v>4584.65</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>67167.33</v>
+        <v>67514.21000000001</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3549.87</v>
+        <v>3574.93</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3861.93</v>
+        <v>3812.01</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>10916.5</v>
+        <v>10777.84</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>7499.15</v>
+        <v>7403.89</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>801.6900000000001</v>
+        <v>791.5</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>26835.32</v>
+        <v>26494.45</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1462.88</v>
+        <v>1448.33</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>819.74</v>
+        <v>811.58</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>1072.32</v>
+        <v>1061.65</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>4096.03</v>
+        <v>4055.28</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>1914.82</v>
+        <v>1907.96</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>3156.95</v>
+        <v>3150.11</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>16755</v>
+        <v>16718.74</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2949.43</v>
+        <v>2937.06</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2339.7</v>
+        <v>2329.89</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>50501.06</v>
+        <v>49916.6</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>923.02</v>
+        <v>912.34</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>31467.68</v>
+        <v>31201.12</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6128.19</v>
+        <v>6123.26</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>4286.28</v>
+        <v>4305.7</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>7130.94</v>
+        <v>7163.25</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>11758.43</v>
+        <v>11811.71</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>16039.76</v>
+        <v>16082.3</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>59760.75</v>
+        <v>59919.22</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>41526.15</v>
+        <v>41467.9</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>8105.32</v>
+        <v>8209.469999999999</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3952.68</v>
+        <v>3974.3</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>29150.1</v>
+        <v>29309.51</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>14368.29</v>
+        <v>14446.87</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2796.26</v>
+        <v>2760.12</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>1326.44</v>
+        <v>1326.45</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>1075.3</v>
+        <v>1076.79</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3958.51</v>
+        <v>3955.81</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1886.03</v>
+        <v>1879.56</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>15960.62</v>
+        <v>15905.84</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>1682.76</v>
+        <v>1676.98</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>4565.66</v>
+        <v>4537.05</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>3851.39</v>
+        <v>3903.25</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1634.57</v>
+        <v>1659.46</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>9559.41</v>
+        <v>9704.940000000001</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>7602.71</v>
+        <v>7718.46</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2343.41</v>
+        <v>2400.39</v>
       </c>
     </row>
     <row r="66">
@@ -4473,13 +4473,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>9315.75</v>
+        <v>9598.23</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>3537-69-CM26</t>
+          <t>5413-110-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4499,17 +4499,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES BLUBOX SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.616.388-2</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
@@ -4534,13 +4534,13 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>7177.11</v>
+        <v>6592.33</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>5413-110-CM26</t>
+          <t>3537-69-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4560,17 +4560,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES BLUBOX SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.616.388-2</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K68" t="inlineStr"/>
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>6615.88</v>
+        <v>7151.55</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2332-119-CM26</t>
+          <t>2852-49-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4626,12 +4626,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -4641,12 +4641,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4656,13 +4656,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>16736.92</v>
+        <v>2449.09</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4132-19-CM26</t>
+          <t>2289-114-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4682,17 +4682,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - X Zona Los Lagos</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -4702,12 +4702,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4717,13 +4717,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1787.71</v>
+        <v>1338.63</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2289-114-CM26</t>
+          <t>4132-19-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4743,17 +4743,17 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>Carabineros de Chile - X Zona Los Lagos</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>1348.73</v>
+        <v>1774.33</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2852-49-CM26</t>
+          <t>2332-119-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4824,12 +4824,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.178.855-8</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>2467.56</v>
+        <v>16611.66</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>36832.61</v>
+        <v>36933.73</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>2275.14</v>
+        <v>2295.4</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>3028.98</v>
+        <v>3055.96</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>37962.81</v>
+        <v>37923.66</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>1532.19</v>
+        <v>1529.94</v>
       </c>
     </row>
     <row r="78">
@@ -5205,13 +5205,13 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>1272.77</v>
+        <v>1270.9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2289-214-CM26</t>
+          <t>1894-5-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5236,12 +5236,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5266,13 +5266,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8098.77</v>
+        <v>77342.52</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1894-5-CM26</t>
+          <t>2289-214-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5312,12 +5312,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>77766.00999999999</v>
+        <v>8054.67</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>9696.959999999999</v>
+        <v>9644.16</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>78715.98</v>
+        <v>78252.11</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2740.69</v>
+        <v>2754.88</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>5773.16</v>
+        <v>5778.72</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>20589.65</v>
+        <v>20444.34</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>6305.68</v>
+        <v>6261.18</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>777.95</v>
+        <v>792.05</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4158.22</v>
+        <v>4233.62</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>878.22</v>
+        <v>894.14</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1625.46</v>
+        <v>1654.93</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>5542.57</v>
+        <v>5629.39</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>3076.05</v>
+        <v>3124.24</v>
       </c>
     </row>
     <row r="93">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>40158.19</v>
+        <v>40787.25</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1126922-170-CM26</t>
+          <t>387-159-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6146,17 +6146,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
@@ -6181,13 +6181,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>13031.72</v>
+        <v>1549.72</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>387-159-CM26</t>
+          <t>1126922-170-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6207,17 +6207,17 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>1549.8</v>
+        <v>13031.05</v>
       </c>
     </row>
     <row r="96">
@@ -6303,13 +6303,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>2828.19</v>
+        <v>2815.54</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>707425-40-CM26</t>
+          <t>2852-139-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6334,12 +6334,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -6349,12 +6349,12 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>BIKE RED MACHINE SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>76.856.309-8</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
@@ -6364,13 +6364,13 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>34612.14</v>
+        <v>3224.39</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2852-139-CM26</t>
+          <t>707425-40-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -6410,12 +6410,12 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>BIKE RED MACHINE SPA</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.856.309-8</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3221.61</v>
+        <v>34641.96</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>17912.26</v>
+        <v>17986.25</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>2454.56</v>
+        <v>2464.7</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4111.87</v>
+        <v>4100.52</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>4806.6</v>
+        <v>4793.34</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>5885.19</v>
+        <v>5817.25</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2116</v>
+        <v>2091.57</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>1467.61</v>
+        <v>1459.18</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>15936.93</v>
+        <v>15845.38</v>
       </c>
     </row>
     <row r="107">
@@ -6974,13 +6974,13 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>1027.57</v>
+        <v>1020.99</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2324-401-CM26</t>
+          <t>2852-183-CM26</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K108" t="inlineStr"/>
@@ -7035,13 +7035,13 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>10802.54</v>
+        <v>2565.67</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2852-183-CM26</t>
+          <t>2324-401-CM26</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K109" t="inlineStr"/>
@@ -7096,13 +7096,13 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>2603.34</v>
+        <v>10646.26</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2306-133-CM26</t>
+          <t>2852-191-CM26</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -7122,17 +7122,17 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -7142,12 +7142,12 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K110" t="inlineStr"/>
@@ -7157,13 +7157,13 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>8786.629999999999</v>
+        <v>5651.44</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>5413-222-CM26</t>
+          <t>2852-190-CM26</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -7183,17 +7183,17 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -7203,12 +7203,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SEGURYCEL SA</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>99.510.910-7</t>
         </is>
       </c>
       <c r="K111" t="inlineStr"/>
@@ -7218,13 +7218,13 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>3334.97</v>
+        <v>3911.3</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2852-190-CM26</t>
+          <t>2306-133-CM26</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -7244,17 +7244,17 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>SEGURYCEL SA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>99.510.910-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K112" t="inlineStr"/>
@@ -7279,13 +7279,13 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>3997.3</v>
+        <v>8597.59</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2852-191-CM26</t>
+          <t>5413-222-CM26</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -7305,17 +7305,17 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -7325,12 +7325,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K113" t="inlineStr"/>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>5775.71</v>
+        <v>3263.22</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>5034.25</v>
+        <v>4917.11</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>16618.4</v>
+        <v>16231.71</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>10615.81</v>
+        <v>10277.3</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>2501.02</v>
+        <v>2421.27</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>2134.93</v>
+        <v>2092.82</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>4868.75</v>
+        <v>4772.74</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>14260.09</v>
+        <v>13884.57</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>825.1</v>
+        <v>803.38</v>
       </c>
     </row>
     <row r="122">
@@ -7889,13 +7889,13 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3629</v>
+        <v>3563.19</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2852-235-CM26</t>
+          <t>707425-59-CM26</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K123" t="inlineStr"/>
@@ -7950,13 +7950,13 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>1423.09</v>
+        <v>2248.2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>707425-59-CM26</t>
+          <t>2852-238-CM26</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K124" t="inlineStr"/>
@@ -8011,13 +8011,13 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>2310.05</v>
+        <v>1433.59</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2852-238-CM26</t>
+          <t>2852-235-CM26</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K125" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>1473.03</v>
+        <v>1384.98</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>3975.85</v>
+        <v>3987.42</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>783.1900000000001</v>
+        <v>786.45</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2875.31</v>
+        <v>2910.7</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>6548.71</v>
+        <v>6629.31</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>9690.52</v>
+        <v>9816.98</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>1669.69</v>
+        <v>1710.78</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>7368.86</v>
+        <v>7508.23</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>2947.55</v>
+        <v>3003.29</v>
       </c>
     </row>
     <row r="134">
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>138463.74</v>
+        <v>139711.06</v>
       </c>
     </row>
     <row r="135">
@@ -8686,7 +8686,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>8749.33</v>
+        <v>8805.290000000001</v>
       </c>
     </row>
     <row r="136">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>4724.77</v>
+        <v>4704.47</v>
       </c>
     </row>
     <row r="137">
@@ -8808,7 +8808,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1060.31</v>
+        <v>1051.27</v>
       </c>
     </row>
     <row r="138">
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2764.19</v>
+        <v>2779.08</v>
       </c>
     </row>
     <row r="139">
@@ -8930,7 +8930,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>786.74</v>
+        <v>795.54</v>
       </c>
     </row>
     <row r="140">
@@ -8991,7 +8991,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>3252.6</v>
+        <v>3277.23</v>
       </c>
     </row>
     <row r="141">
@@ -9052,7 +9052,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>6615.25</v>
+        <v>6640.31</v>
       </c>
     </row>
     <row r="142">
@@ -9113,7 +9113,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>4041.4</v>
+        <v>4056.71</v>
       </c>
     </row>
     <row r="143">
@@ -9174,7 +9174,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>839.5</v>
+        <v>842.6799999999999</v>
       </c>
     </row>
     <row r="144">
@@ -9235,7 +9235,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>1243.51</v>
+        <v>1240.37</v>
       </c>
     </row>
     <row r="145">
@@ -9296,7 +9296,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>2175.26</v>
+        <v>2169.77</v>
       </c>
     </row>
     <row r="146">
@@ -9357,7 +9357,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>2856.27</v>
+        <v>2849.06</v>
       </c>
     </row>
     <row r="147">
@@ -9418,13 +9418,13 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>18010.92</v>
+        <v>18145.1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2328-505-CM26</t>
+          <t>1126922-574-CM26</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -9449,12 +9449,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9464,12 +9464,12 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.203.369-9</t>
         </is>
       </c>
       <c r="K148" t="inlineStr"/>
@@ -9479,13 +9479,13 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>16625.13</v>
+        <v>2585.32</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1126922-574-CM26</t>
+          <t>2328-505-CM26</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -9510,12 +9510,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -9525,12 +9525,12 @@
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>77.203.369-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K149" t="inlineStr"/>
@@ -9540,13 +9540,13 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>2611.37</v>
+        <v>16459.33</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2328-512-CM26</t>
+          <t>2289-505-CM26</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K150" t="inlineStr"/>
@@ -9601,13 +9601,13 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>6973.02</v>
+        <v>1331.77</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2289-505-CM26</t>
+          <t>3289-60-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -9627,17 +9627,17 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9647,12 +9647,12 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.203.369-9</t>
         </is>
       </c>
       <c r="K151" t="inlineStr"/>
@@ -9662,13 +9662,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>1337.63</v>
+        <v>785.87</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>3289-60-CM26</t>
+          <t>2328-512-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -9693,12 +9693,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -9708,12 +9708,12 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>77.203.369-9</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K152" t="inlineStr"/>
@@ -9723,7 +9723,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>789.33</v>
+        <v>6942.45</v>
       </c>
     </row>
     <row r="153">
@@ -9784,7 +9784,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>1181.2</v>
+        <v>1168.35</v>
       </c>
     </row>
     <row r="154">
@@ -9845,7 +9845,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>4993.37</v>
+        <v>4939.06</v>
       </c>
     </row>
     <row r="155">
@@ -9906,7 +9906,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3889.61</v>
+        <v>3847.3</v>
       </c>
     </row>
     <row r="156">
@@ -9967,7 +9967,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>1867.01</v>
+        <v>1846.7</v>
       </c>
     </row>
     <row r="157">
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>9408.879999999999</v>
+        <v>9387.52</v>
       </c>
     </row>
     <row r="158">
@@ -10089,13 +10089,13 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2192.44</v>
+        <v>2187.46</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2852-448-CM26</t>
+          <t>1116005-45-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10120,12 +10120,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -10135,12 +10135,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>SEGURYCEL SA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>99.510.910-7</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K159" t="inlineStr"/>
@@ -10150,13 +10150,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>1829.48</v>
+        <v>923.87</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1116005-45-CM26</t>
+          <t>2297-659-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10176,17 +10176,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K160" t="inlineStr"/>
@@ -10211,13 +10211,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>919.36</v>
+        <v>8833.52</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2297-659-CM26</t>
+          <t>2852-448-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10237,17 +10237,17 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>SEGURYCEL SA</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>99.510.910-7</t>
         </is>
       </c>
       <c r="K161" t="inlineStr"/>
@@ -10272,13 +10272,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>8790.34</v>
+        <v>1838.47</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2297-678-CM26</t>
+          <t>2297-677-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>COMERCIAL JOAQUIN LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.288.097-0</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K162" t="inlineStr"/>
@@ -10333,13 +10333,13 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>4242.54</v>
+        <v>6349.47</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2297-677-CM26</t>
+          <t>2297-678-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10379,12 +10379,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL JOAQUIN LIMITADA</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.288.097-0</t>
         </is>
       </c>
       <c r="K163" t="inlineStr"/>
@@ -10394,7 +10394,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>6329.32</v>
+        <v>4256.04</v>
       </c>
     </row>
     <row r="164">
@@ -10455,13 +10455,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>3208.86</v>
+        <v>3225.92</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1057532-814-CM26</t>
+          <t>1336-103-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>BIKE RED MACHINE SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>76.856.309-8</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K165" t="inlineStr"/>
@@ -10516,13 +10516,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>7666.5</v>
+        <v>9058.879999999999</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2852-489-CM26</t>
+          <t>1057532-814-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -10547,12 +10547,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10562,12 +10562,12 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>BIKE RED MACHINE SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.856.309-8</t>
         </is>
       </c>
       <c r="K166" t="inlineStr"/>
@@ -10577,13 +10577,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>961.76</v>
+        <v>7776.21</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1336-103-CM26</t>
+          <t>2852-489-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -10603,17 +10603,17 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -10623,12 +10623,12 @@
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K167" t="inlineStr"/>
@@ -10638,7 +10638,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>8931.08</v>
+        <v>975.52</v>
       </c>
     </row>
     <row r="168">
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>3995.39</v>
+        <v>4062.97</v>
       </c>
     </row>
     <row r="169">
@@ -10760,7 +10760,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>22469.25</v>
+        <v>22849.26</v>
       </c>
     </row>
     <row r="170">
@@ -10821,7 +10821,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>15975.78</v>
+        <v>16138.25</v>
       </c>
     </row>
     <row r="171">
@@ -10882,7 +10882,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>15593.27</v>
+        <v>15751.84</v>
       </c>
     </row>
     <row r="172">
@@ -10943,7 +10943,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>855.4</v>
+        <v>863.42</v>
       </c>
     </row>
     <row r="173">
@@ -11004,13 +11004,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>6444.84</v>
+        <v>6505.28</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2289-535-CM26</t>
+          <t>2289-532-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11050,12 +11050,12 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K174" t="inlineStr"/>
@@ -11065,13 +11065,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>1810.59</v>
+        <v>5050.48</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1126922-738-CM26</t>
+          <t>2289-535-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11091,17 +11091,17 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -11111,12 +11111,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>77.203.369-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K175" t="inlineStr"/>
@@ -11126,13 +11126,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>1739.19</v>
+        <v>1796.85</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>2289-532-CM26</t>
+          <t>1126922-738-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11152,17 +11152,17 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.203.369-9</t>
         </is>
       </c>
       <c r="K176" t="inlineStr"/>
@@ -11187,7 +11187,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>5089.09</v>
+        <v>1726</v>
       </c>
     </row>
     <row r="177">
@@ -11248,13 +11248,13 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>795.51</v>
+        <v>790.58</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>3479-926-CM26</t>
+          <t>2328-689-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11279,12 +11279,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>69.220.600-2</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11294,12 +11294,12 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>BROKER SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>77.819.582-8</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K178" t="inlineStr"/>
@@ -11309,13 +11309,13 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>22990.69</v>
+        <v>7762.61</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2328-686-CM26</t>
+          <t>2328-688-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K179" t="inlineStr"/>
@@ -11370,13 +11370,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>18094.33</v>
+        <v>27492.4</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>2328-687-CM26</t>
+          <t>2328-686-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11396,7 +11396,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -11431,13 +11431,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>18370.89</v>
+        <v>18363.76</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>2328-688-CM26</t>
+          <t>3479-926-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11462,12 +11462,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.600-2</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>BROKER SPA</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.819.582-8</t>
         </is>
       </c>
       <c r="K181" t="inlineStr"/>
@@ -11492,13 +11492,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>27089.03</v>
+        <v>23333.03</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>2328-689-CM26</t>
+          <t>2328-687-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -11553,13 +11553,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>7648.72</v>
+        <v>18644.44</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>2297-790-CM26</t>
+          <t>1173430-89-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -11579,17 +11579,17 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.950.500-K</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>Centro de Educación y Trabajo de Osorno</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -11614,13 +11614,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>8659.459999999999</v>
+        <v>2088.66</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1173430-89-CM26</t>
+          <t>2297-786-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11640,17 +11640,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.950.500-K</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Centro de Educación y Trabajo de Osorno</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -11660,12 +11660,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11675,13 +11675,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2042.59</v>
+        <v>1639.32</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>2297-786-CM26</t>
+          <t>2328-713-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -11736,13 +11736,13 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>1603.17</v>
+        <v>66284.83</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>2328-713-CM26</t>
+          <t>5413-586-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -11767,12 +11767,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -11782,12 +11782,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -11797,13 +11797,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>64822.91</v>
+        <v>855.66</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5413-586-CM26</t>
+          <t>2324-833-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -11823,17 +11823,17 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K187" t="inlineStr"/>
@@ -11858,13 +11858,13 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>836.79</v>
+        <v>813.97</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>2324-833-CM26</t>
+          <t>2297-790-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -11884,17 +11884,17 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -11904,12 +11904,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K188" t="inlineStr"/>
@@ -11919,13 +11919,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>796.02</v>
+        <v>8854.76</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>2852-561-CM26</t>
+          <t>1413-558-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -11950,12 +11950,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.004.098-5</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -11965,12 +11965,12 @@
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K189" t="inlineStr"/>
@@ -11980,13 +11980,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>1080.04</v>
+        <v>1114.4</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1413-558-CM26</t>
+          <t>2852-561-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12011,12 +12011,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>61.004.098-5</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K190" t="inlineStr"/>
@@ -12041,13 +12041,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>1106.76</v>
+        <v>1087.49</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1413-581-CM26</t>
+          <t>4832-367-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.004.098-5</t>
+          <t>69.252.000-9</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12087,12 +12087,12 @@
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>86.887.200-4</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K191" t="inlineStr"/>
@@ -12102,13 +12102,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>1106.76</v>
+        <v>2250.88</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>4832-367-CM26</t>
+          <t>1413-581-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12133,12 +12133,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>69.252.000-9</t>
+          <t>61.004.098-5</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+          <t>Dirección Regional de Gendarmeria - Puerto Montt</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12148,12 +12148,12 @@
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIALIZADORA DE ART DE PROTECCION Y SEGURIDAD INDUSTRIAL MANQUEHUE</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>86.887.200-4</t>
         </is>
       </c>
       <c r="K192" t="inlineStr"/>
@@ -12163,7 +12163,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2281.27</v>
+        <v>1092.02</v>
       </c>
     </row>
     <row r="193">
@@ -12224,7 +12224,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>895.46</v>
+        <v>877.9400000000001</v>
       </c>
     </row>
     <row r="194">
@@ -12285,7 +12285,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>3769.87</v>
+        <v>3696.08</v>
       </c>
     </row>
     <row r="195">
@@ -12346,7 +12346,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>1420</v>
+        <v>1425.54</v>
       </c>
     </row>
     <row r="196">
@@ -12407,7 +12407,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>2762.1</v>
+        <v>2789.88</v>
       </c>
     </row>
     <row r="197">
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>4033.96</v>
+        <v>4074.53</v>
       </c>
     </row>
     <row r="198">
@@ -12529,7 +12529,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3360.74</v>
+        <v>3394.39</v>
       </c>
     </row>
     <row r="199">
@@ -12590,7 +12590,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>5446.41</v>
+        <v>5500.95</v>
       </c>
     </row>
     <row r="200">
@@ -12651,7 +12651,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>1591.4</v>
+        <v>1599.51</v>
       </c>
     </row>
     <row r="201">
@@ -12712,7 +12712,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>3827.25</v>
+        <v>3807.86</v>
       </c>
     </row>
     <row r="202">
@@ -12773,7 +12773,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>3518.77</v>
+        <v>3500.94</v>
       </c>
     </row>
     <row r="203">
@@ -12834,7 +12834,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>43395.69</v>
+        <v>43488.18</v>
       </c>
     </row>
     <row r="204">
@@ -12895,7 +12895,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>4990.2</v>
+        <v>5000.84</v>
       </c>
     </row>
     <row r="205">
@@ -12956,7 +12956,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>3828.88</v>
+        <v>3853.84</v>
       </c>
     </row>
     <row r="206">
@@ -13017,7 +13017,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>3367.72</v>
+        <v>3375.45</v>
       </c>
     </row>
     <row r="207">
@@ -13078,7 +13078,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>7906.98</v>
+        <v>7925.11</v>
       </c>
     </row>
     <row r="208">
@@ -13139,7 +13139,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>24775.29</v>
+        <v>24832.11</v>
       </c>
     </row>
     <row r="209">
@@ -13200,7 +13200,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>3066.06</v>
+        <v>3086.58</v>
       </c>
     </row>
     <row r="210">
@@ -13261,7 +13261,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>33489.74</v>
+        <v>33713.91</v>
       </c>
     </row>
     <row r="211">
@@ -13322,7 +13322,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>22462.77</v>
+        <v>22613.13</v>
       </c>
     </row>
     <row r="212">
@@ -13383,7 +13383,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>1536.43</v>
+        <v>1533.35</v>
       </c>
     </row>
     <row r="213">
@@ -13444,7 +13444,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>1643.71</v>
+        <v>1634.2</v>
       </c>
     </row>
     <row r="214">
@@ -13505,7 +13505,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>3338.12</v>
+        <v>3299.27</v>
       </c>
     </row>
     <row r="215">
@@ -13566,7 +13566,190 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>38109.25</v>
+        <v>37921.88</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>2852-800-CM26</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>69.220.200-7</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>COMERCIAL GRAN VIA SPA</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="n">
+        <v>1839.79</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>2324-1155-CM26</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>69.220.100-0</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>DAT I GES SPA</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="n">
+        <v>15005.63</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>1037-89-CM26</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M218" s="2" t="n">
+        <v>3780.1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-lagos.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-lagos.xlsx
@@ -806,7 +806,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +993,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1241,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1489,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2046,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2091,7 +2111,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2335,7 +2359,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2518,7 +2546,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2794,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2945,7 +2981,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3107,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3294,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3359,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +3912,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4099,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4469,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4592,7 +4656,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4653,7 +4721,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4714,7 +4786,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5019,7 +5095,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5080,7 +5160,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5263,7 +5347,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5446,7 +5534,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5507,7 +5599,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5568,7 +5664,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5629,7 +5729,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5690,7 +5794,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5751,7 +5859,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5812,7 +5924,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5995,7 +6111,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6056,7 +6176,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6117,7 +6241,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6178,7 +6306,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6239,7 +6371,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6422,7 +6558,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6483,7 +6623,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6544,7 +6688,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6605,7 +6753,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6666,7 +6818,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6727,7 +6883,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6849,7 +7009,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6910,7 +7074,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6971,7 +7139,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7459,7 +7631,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7520,7 +7696,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +7883,11 @@
           <t>77.362.622-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8558,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8745,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +8871,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +8936,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9001,11 @@
           <t>77.798.686-4</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8862,7 +9066,11 @@
           <t>77.809.872-5</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9192,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9562,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +9810,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +9875,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10611,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10692,7 +10920,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10814,7 +11046,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11172,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11058,7 +11298,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11363,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11363,7 +11611,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +11737,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +11802,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11607,7 +11867,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12054,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12180,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12306,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12432,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12497,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +12562,11 @@
           <t>77.173.807-9</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12339,7 +12627,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +12753,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +12818,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +12944,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13009,11 @@
           <t>77.512.806-2</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13196,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13261,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13326,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +13574,11 @@
           <t>76.193.188-1</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +13761,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13681,7 +14009,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14135,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14200,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14387,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +14696,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15005,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15192,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14901,7 +15257,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15206,7 +15566,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15267,7 +15631,11 @@
           <t>77.414.534-6</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15450,7 +15818,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +15883,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16253,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15999,7 +16379,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +16444,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16121,7 +16509,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +16696,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +16761,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16731,7 +17131,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17257,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17322,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17036,7 +17448,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17341,7 +17757,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18005,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17890,7 +18314,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18195,7 +18623,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +18688,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +18753,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +18940,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18561,7 +19005,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +19314,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18927,7 +19379,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19171,7 +19627,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +19692,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +19757,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +19822,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20009,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19598,7 +20074,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20200,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20265,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +20452,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20025,7 +20517,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20208,7 +20704,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20269,7 +20769,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +20895,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20452,7 +20960,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20696,7 +21208,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20757,7 +21273,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +21338,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21249,7 +21773,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21371,7 +21899,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21432,7 +21964,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21737,7 +22273,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21920,7 +22460,11 @@
           <t>77.601.267-K</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22042,7 +22586,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22103,7 +22651,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22408,7 +22960,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22591,7 +23147,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23018,7 +23578,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23079,7 +23643,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23262,7 +23830,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23323,7 +23895,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23384,7 +23960,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23445,7 +24025,11 @@
           <t>77.795.374-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23506,7 +24090,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23628,7 +24216,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23811,7 +24403,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23872,7 +24468,11 @@
           <t>77.819.582-8</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23933,7 +24533,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23994,7 +24598,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24055,7 +24663,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24116,7 +24728,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24177,7 +24793,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24238,7 +24858,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24360,7 +24984,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24543,7 +25171,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24665,7 +25297,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24848,7 +25484,11 @@
           <t>77.610.398-5</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24909,7 +25549,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25031,7 +25675,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25153,7 +25801,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25214,7 +25866,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25275,7 +25931,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25336,7 +25996,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25458,7 +26122,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25519,7 +26187,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25580,7 +26252,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25641,7 +26317,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25763,7 +26443,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25824,7 +26508,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25946,7 +26634,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26007,7 +26699,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26129,7 +26825,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26190,7 +26890,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26312,7 +27016,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26373,7 +27081,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26495,7 +27207,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26556,7 +27272,11 @@
           <t>77.601.801-5</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26617,7 +27337,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26678,7 +27402,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26739,7 +27467,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26800,7 +27532,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26983,7 +27719,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27044,7 +27784,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27105,7 +27849,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27471,7 +28219,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27837,7 +28589,11 @@
           <t>76.856.309-8</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27898,7 +28654,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28020,7 +28780,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28081,7 +28845,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28142,7 +28910,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28325,7 +29097,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28386,7 +29162,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28447,7 +29227,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28508,7 +29292,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28569,7 +29357,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28630,7 +29422,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28691,7 +29487,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28874,7 +29674,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28935,7 +29739,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28996,7 +29804,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29118,7 +29930,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29179,7 +29995,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29240,7 +30060,11 @@
           <t>77.831.858-K</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29362,7 +30186,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29423,7 +30251,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29606,7 +30438,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-lagos.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-lagos.xlsx
@@ -871,7 +871,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3424,7 +3428,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13639,7 +13647,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14265,7 +14277,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15383,7 +15399,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18440,7 +18460,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21147,7 +21171,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-lagos.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-lagos.xlsx
@@ -979,7 +979,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>COMANDO DE APOYO A LA FUERZA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -19127,7 +19127,7 @@
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -24728,7 +24728,7 @@
       </c>
       <c r="E388" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F388" t="inlineStr">
@@ -24793,7 +24793,7 @@
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
@@ -26057,7 +26057,7 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
@@ -26122,7 +26122,7 @@
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
@@ -26508,7 +26508,7 @@
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
@@ -26573,7 +26573,7 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
@@ -26825,7 +26825,7 @@
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
@@ -26890,7 +26890,7 @@
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
@@ -27467,7 +27467,7 @@
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
@@ -27784,7 +27784,7 @@
       </c>
       <c r="E436" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F436" t="inlineStr">

--- a/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-lagos.xlsx
+++ b/docs/oc-regiones/productos-y-servicios-de-ferreteria/los-lagos.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M499"/>
+  <dimension ref="A1:M500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3315,7 +3315,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>1301-35-CM25</t>
+          <t>2328-214-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3340,12 +3340,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -3355,17 +3355,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL AGUSTIN LIMITADA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.287.853-4</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3374,7 +3374,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>1552.62</v>
+        <v>1249.59</v>
       </c>
     </row>
     <row r="48">
@@ -3441,7 +3441,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2328-214-CM25</t>
+          <t>1301-35-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -3481,17 +3481,17 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>COMERCIAL AGUSTIN LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.287.853-4</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3500,7 +3500,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1249.59</v>
+        <v>1552.62</v>
       </c>
     </row>
     <row r="50">
@@ -4933,7 +4933,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2297-546-CM25</t>
+          <t>2297-544-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>1020.87</v>
+        <v>994.12</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2297-547-CM25</t>
+          <t>2297-546-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5034,32 +5034,28 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4190.04</v>
+        <v>1020.87</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2297-544-CM25</t>
+          <t>2297-547-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5099,22 +5095,26 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>994.12</v>
+        <v>4190.04</v>
       </c>
     </row>
     <row r="76">
@@ -5559,7 +5559,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2297-684-CM25</t>
+          <t>853-232-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5579,17 +5579,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>70.072.600-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5618,13 +5618,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1033.98</v>
+        <v>13092.26</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>853-232-CM25</t>
+          <t>2852-332-CM25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5644,17 +5644,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>70.072.600-2</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>JUNTA NACIONAL DE JARDINES         INFANTILES</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5664,17 +5664,17 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5683,13 +5683,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>13092.26</v>
+        <v>4502.93</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2852-332-CM25</t>
+          <t>2297-684-CM25</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5714,12 +5714,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5748,7 +5748,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>4502.93</v>
+        <v>1033.98</v>
       </c>
     </row>
     <row r="86">
@@ -6136,7 +6136,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>707425-71-CM25</t>
+          <t>2297-804-CM25</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6156,17 +6156,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6195,13 +6195,13 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>2871.18</v>
+        <v>16241.36</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2297-804-CM25</t>
+          <t>707425-71-CM25</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>16241.36</v>
+        <v>2871.18</v>
       </c>
     </row>
     <row r="94">
@@ -7782,7 +7782,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>1426102-161-CM25</t>
+          <t>1426102-163-CM25</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -7822,26 +7822,22 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>77.362.622-7</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>753.8</v>
+        <v>1771.45</v>
       </c>
     </row>
     <row r="119">
@@ -7908,7 +7904,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>1426102-163-CM25</t>
+          <t>1426102-161-CM25</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -7948,22 +7944,26 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIALIZADORA Y ASESORÍAS VICOM SPA</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K120" t="inlineStr"/>
+          <t>77.362.622-7</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>1771.45</v>
+        <v>753.8</v>
       </c>
     </row>
     <row r="121">
@@ -8896,7 +8896,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>1037-100-CM25</t>
+          <t>707425-116-CM25</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -8921,12 +8921,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -8936,17 +8936,17 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>VENTIA SPA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>77.798.686-4</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -8955,13 +8955,13 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>1067.62</v>
+        <v>1322.1</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>707425-116-CM25</t>
+          <t>1037-100-CM25</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -9001,17 +9001,17 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>VENTIA SPA</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
+          <t>77.798.686-4</t>
         </is>
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -9020,7 +9020,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>1322.1</v>
+        <v>1067.62</v>
       </c>
     </row>
     <row r="138">
@@ -9217,7 +9217,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>1126922-1429-CM25</t>
+          <t>707425-125-CM25</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>FUEGOCLIMA SPA</t>
+          <t xml:space="preserve">Seguridad Industrial SPA </t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
         <is>
-          <t>77.190.725-3</t>
+          <t>76.756.768-5</t>
         </is>
       </c>
       <c r="K141" t="inlineStr"/>
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>3331.69</v>
+        <v>3092.83</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>707425-125-CM25</t>
+          <t>707425-126-CM25</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -9318,12 +9318,12 @@
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seguridad Industrial SPA </t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
         <is>
-          <t>76.756.768-5</t>
+          <t>77.084.730-3</t>
         </is>
       </c>
       <c r="K142" t="inlineStr"/>
@@ -9333,13 +9333,13 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3092.83</v>
+        <v>8280.790000000001</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>707425-126-CM25</t>
+          <t>2324-1112-CM25</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
+          <t>14.205.876-6</t>
         </is>
       </c>
       <c r="K143" t="inlineStr"/>
@@ -9394,13 +9394,13 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>8280.790000000001</v>
+        <v>6859.51</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2324-1112-CM25</t>
+          <t>1126922-1429-CM25</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -9425,12 +9425,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -9440,12 +9440,12 @@
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>FUEGOCLIMA SPA</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
+          <t>77.190.725-3</t>
         </is>
       </c>
       <c r="K144" t="inlineStr"/>
@@ -9455,7 +9455,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>6859.51</v>
+        <v>3331.69</v>
       </c>
     </row>
     <row r="145">
@@ -10022,7 +10022,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2289-804-CM25</t>
+          <t>2297-1204-CM25</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10047,12 +10047,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -10077,13 +10077,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>1063.02</v>
+        <v>6325.39</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2297-1204-CM25</t>
+          <t>2289-804-CM25</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10138,7 +10138,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>6325.39</v>
+        <v>1063.02</v>
       </c>
     </row>
     <row r="156">
@@ -11892,7 +11892,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1860-81-CM25</t>
+          <t>1860-80-CM25</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>SEGURYCEL SA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>99.510.910-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K184" t="inlineStr"/>
@@ -11947,13 +11947,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>1575.83</v>
+        <v>2891.9</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1860-80-CM25</t>
+          <t>1860-81-CM25</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -11993,12 +11993,12 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SEGURYCEL SA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>99.510.910-7</t>
         </is>
       </c>
       <c r="K185" t="inlineStr"/>
@@ -12008,7 +12008,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>2891.9</v>
+        <v>1575.83</v>
       </c>
     </row>
     <row r="186">
@@ -13477,7 +13477,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2289-990-CM25</t>
+          <t>3443-941-CM25</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13502,12 +13502,12 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -13517,12 +13517,12 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>COMERCIAL MALMO S.A.</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
+          <t>76.123.414-5</t>
         </is>
       </c>
       <c r="K209" t="inlineStr"/>
@@ -13532,13 +13532,13 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>1644.28</v>
+        <v>2801.43</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3443-941-CM25</t>
+          <t>2289-990-CM25</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13563,12 +13563,12 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
@@ -13578,12 +13578,12 @@
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>COMERCIAL MALMO S.A.</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>76.123.414-5</t>
+          <t>76.397.758-7</t>
         </is>
       </c>
       <c r="K210" t="inlineStr"/>
@@ -13593,7 +13593,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>2801.43</v>
+        <v>1644.28</v>
       </c>
     </row>
     <row r="211">
@@ -15538,7 +15538,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1002-510-CM25</t>
+          <t>796290-168-CM25</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -15558,17 +15558,17 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -15578,17 +15578,17 @@
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>QUIMICA ANDINA CHILE S.A.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>77.414.534-6</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -15597,13 +15597,13 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>49916.6</v>
+        <v>912.34</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>796290-168-CM25</t>
+          <t>1002-510-CM25</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -15623,17 +15623,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -15643,17 +15643,17 @@
       </c>
       <c r="I243" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>QUIMICA ANDINA CHILE S.A.</t>
         </is>
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.414.534-6</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
@@ -15662,7 +15662,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>912.34</v>
+        <v>49916.6</v>
       </c>
     </row>
     <row r="244">
@@ -15729,7 +15729,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>437-101-CM25</t>
+          <t>2289-1100-CM25</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -15754,12 +15754,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -15769,32 +15769,28 @@
       </c>
       <c r="I245" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.397.758-7</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>3519.17</v>
+        <v>6123.26</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>2289-1100-CM25</t>
+          <t>437-101-CM25</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -15819,12 +15815,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15834,22 +15830,26 @@
       </c>
       <c r="I246" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J246" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>6123.26</v>
+        <v>3519.17</v>
       </c>
     </row>
     <row r="247">
@@ -17103,7 +17103,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>3537-57-CM26</t>
+          <t>2297-41-CM26</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -17123,17 +17123,17 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -17162,13 +17162,13 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>7718.46</v>
+        <v>1659.46</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>2297-41-CM26</t>
+          <t>2297-42-CM26</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -17208,32 +17208,28 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>BLOOMBERRY COMERCIAL SPA</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.330.742-5</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>1659.46</v>
+        <v>9704.940000000001</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>2297-42-CM26</t>
+          <t>3537-57-CM26</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -17253,17 +17249,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -17273,22 +17269,26 @@
       </c>
       <c r="I269" t="inlineStr">
         <is>
-          <t>BLOOMBERRY COMERCIAL SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J269" t="inlineStr">
         <is>
-          <t>76.330.742-5</t>
-        </is>
-      </c>
-      <c r="K269" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>9704.940000000001</v>
+        <v>7718.46</v>
       </c>
     </row>
     <row r="270">
@@ -17420,7 +17420,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>5413-110-CM26</t>
+          <t>3537-69-CM26</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -17440,17 +17440,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>61.101.037-0</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -17460,28 +17460,32 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES BLUBOX SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>76.616.388-2</t>
-        </is>
-      </c>
-      <c r="K272" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>6592.33</v>
+        <v>7151.55</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>3537-69-CM26</t>
+          <t>5413-110-CM26</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -17501,17 +17505,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>61.101.037-0</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -17521,32 +17525,28 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES BLUBOX SPA</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.616.388-2</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>7151.55</v>
+        <v>6592.33</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>4132-19-CM26</t>
+          <t>2289-114-CM26</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -17566,17 +17566,17 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -17586,12 +17586,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K274" t="inlineStr"/>
@@ -17601,13 +17601,13 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>1774.33</v>
+        <v>1338.63</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>2332-119-CM26</t>
+          <t>2852-49-CM26</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -17632,12 +17632,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17647,28 +17647,32 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>76.178.855-8</t>
-        </is>
-      </c>
-      <c r="K275" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>16611.66</v>
+        <v>2449.09</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>2289-114-CM26</t>
+          <t>4132-19-CM26</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -17688,17 +17692,17 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -17708,12 +17712,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K276" t="inlineStr"/>
@@ -17723,13 +17727,13 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>1338.63</v>
+        <v>1774.33</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>2852-49-CM26</t>
+          <t>2332-119-CM26</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -17754,12 +17758,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17769,26 +17773,22 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>SOCIEDAD PROCESADORA DE PARTES Y PIEZAS LIMITADA</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.178.855-8</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>2449.09</v>
+        <v>16611.66</v>
       </c>
     </row>
     <row r="278">
@@ -18916,7 +18916,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>796290-13-CM26</t>
+          <t>507428-272-CM26</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -18941,12 +18941,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -18956,17 +18956,17 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL TRANCURA SPA</t>
         </is>
       </c>
       <c r="J296" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.823.479-3</t>
         </is>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -18975,13 +18975,13 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>5629.39</v>
+        <v>3124.24</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1079639-135-CM26</t>
+          <t>796290-13-CM26</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -19006,12 +19006,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>61.979.300-5</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -19021,28 +19021,32 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J297" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
-        </is>
-      </c>
-      <c r="K297" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>40787.25</v>
+        <v>5629.39</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>507428-272-CM26</t>
+          <t>1079639-135-CM26</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -19067,12 +19071,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>61.979.300-5</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -19082,32 +19086,28 @@
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t>COMERCIAL TRANCURA SPA</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J298" t="inlineStr">
         <is>
-          <t>77.823.479-3</t>
-        </is>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>Biobío</t>
-        </is>
-      </c>
+          <t>96.803.460-k</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr"/>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3124.24</v>
+        <v>40787.25</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1126922-170-CM26</t>
+          <t>387-159-CM26</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -19132,12 +19132,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -19147,12 +19147,12 @@
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J299" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K299" t="inlineStr"/>
@@ -19162,13 +19162,13 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>13031.05</v>
+        <v>1549.72</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>387-159-CM26</t>
+          <t>1126922-170-CM26</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -19193,12 +19193,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -19208,12 +19208,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K300" t="inlineStr"/>
@@ -19223,7 +19223,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>1549.72</v>
+        <v>13031.05</v>
       </c>
     </row>
     <row r="301">
@@ -20367,7 +20367,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>2852-198-CM26</t>
+          <t>2852-199-CM26</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -20407,32 +20407,28 @@
       </c>
       <c r="I319" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
         </is>
       </c>
       <c r="J319" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>14.205.876-6</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr"/>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>4917.11</v>
+        <v>16231.71</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>2852-199-CM26</t>
+          <t>2852-198-CM26</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -20472,28 +20468,32 @@
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t>FERNANDO ALBERTO VELOSO OLIVA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J320" t="inlineStr">
         <is>
-          <t>14.205.876-6</t>
-        </is>
-      </c>
-      <c r="K320" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>16231.71</v>
+        <v>4917.11</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>2328-282-CM26</t>
+          <t>2328-283-CM26</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -20533,32 +20533,28 @@
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>LUIS ALEXANDER</t>
         </is>
       </c>
       <c r="J321" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K321" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.962.756-1</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr"/>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>10277.3</v>
+        <v>2421.27</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>2328-283-CM26</t>
+          <t>2328-282-CM26</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -20598,28 +20594,32 @@
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t>LUIS ALEXANDER</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J322" t="inlineStr">
         <is>
-          <t>76.962.756-1</t>
-        </is>
-      </c>
-      <c r="K322" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2421.27</v>
+        <v>10277.3</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>1426102-47-CM26</t>
+          <t>2852-213-CM26</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -20644,12 +20644,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -20659,28 +20659,32 @@
       </c>
       <c r="I323" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J323" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K323" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>2092.82</v>
+        <v>4772.74</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>2852-213-CM26</t>
+          <t>1426102-47-CM26</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -20705,12 +20709,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -20720,32 +20724,28 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J324" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K324" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr"/>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>4772.74</v>
+        <v>2092.82</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>2730-146-CM26</t>
+          <t>1126922-270-CM26</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -20770,12 +20770,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>69.230.400-4</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASTRO</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -20785,32 +20785,28 @@
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>INGENIERIA DE COMBUSTION BOSCA CHILE S A</t>
         </is>
       </c>
       <c r="J325" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K325" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>79.610.100-8</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr"/>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>13884.57</v>
+        <v>803.38</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>1126922-270-CM26</t>
+          <t>2730-146-CM26</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -20835,12 +20831,12 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.230.400-4</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20850,22 +20846,26 @@
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t>INGENIERIA DE COMBUSTION BOSCA CHILE S A</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J326" t="inlineStr">
         <is>
-          <t>79.610.100-8</t>
-        </is>
-      </c>
-      <c r="K326" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>803.38</v>
+        <v>13884.57</v>
       </c>
     </row>
     <row r="327">
@@ -20936,7 +20936,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>2852-235-CM26</t>
+          <t>2852-238-CM26</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -20976,28 +20976,32 @@
       </c>
       <c r="I328" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J328" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K328" t="inlineStr"/>
+          <t>77.537.871-9</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>1384.98</v>
+        <v>1433.59</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>2852-238-CM26</t>
+          <t>707425-59-CM26</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -21022,12 +21026,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -21037,32 +21041,28 @@
       </c>
       <c r="I329" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J329" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
-        </is>
-      </c>
-      <c r="K329" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr"/>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>1433.59</v>
+        <v>2248.2</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>707425-59-CM26</t>
+          <t>2852-235-CM26</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -21087,12 +21087,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -21102,12 +21102,12 @@
       </c>
       <c r="I330" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J330" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.231.391-K</t>
         </is>
       </c>
       <c r="K330" t="inlineStr"/>
@@ -21117,7 +21117,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>2248.2</v>
+        <v>1384.98</v>
       </c>
     </row>
     <row r="331">
@@ -21253,7 +21253,7 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>2289-426-CM26</t>
+          <t>2852-270-CM26</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -21273,17 +21273,17 @@
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -21293,17 +21293,17 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J333" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -21312,13 +21312,13 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>2910.7</v>
+        <v>6629.31</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>2852-270-CM26</t>
+          <t>2289-426-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -21338,17 +21338,17 @@
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -21358,17 +21358,17 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J334" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -21377,7 +21377,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>6629.31</v>
+        <v>2910.7</v>
       </c>
     </row>
     <row r="335">
@@ -22505,7 +22505,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>2328-505-CM26</t>
+          <t>1126922-574-CM26</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -22530,12 +22530,12 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -22545,32 +22545,28 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
         </is>
       </c>
       <c r="J353" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K353" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.203.369-9</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr"/>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>16459.33</v>
+        <v>2585.32</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>1126922-574-CM26</t>
+          <t>2328-505-CM26</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -22595,12 +22591,12 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -22610,28 +22606,32 @@
       </c>
       <c r="I354" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J354" t="inlineStr">
         <is>
-          <t>77.203.369-9</t>
-        </is>
-      </c>
-      <c r="K354" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>2585.32</v>
+        <v>16459.33</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>2289-505-CM26</t>
+          <t>2328-512-CM26</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -22651,17 +22651,17 @@
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -22671,28 +22671,32 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J355" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K355" t="inlineStr"/>
+          <t>77.831.858-K</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>1331.77</v>
+        <v>6942.45</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>3289-60-CM26</t>
+          <t>2289-505-CM26</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -22712,17 +22716,17 @@
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
@@ -22732,12 +22736,12 @@
       </c>
       <c r="I356" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J356" t="inlineStr">
         <is>
-          <t>77.203.369-9</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K356" t="inlineStr"/>
@@ -22747,13 +22751,13 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>785.87</v>
+        <v>1331.77</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>2328-512-CM26</t>
+          <t>3289-60-CM26</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -22778,12 +22782,12 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G357" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H357" t="inlineStr">
@@ -22793,32 +22797,28 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K357" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.203.369-9</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr"/>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>6942.45</v>
+        <v>785.87</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>3481-65-CM26</t>
+          <t>1860-41-CM26</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -22843,12 +22843,12 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>61.101.015-K</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G358" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H358" t="inlineStr">
@@ -22858,32 +22858,28 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J358" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K358" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr"/>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>1168.35</v>
+        <v>4939.06</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>1860-41-CM26</t>
+          <t>1126922-621-CM26</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -22908,12 +22904,12 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -22923,12 +22919,12 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
         </is>
       </c>
       <c r="J359" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
+          <t>77.203.369-9</t>
         </is>
       </c>
       <c r="K359" t="inlineStr"/>
@@ -22938,13 +22934,13 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>4939.06</v>
+        <v>3847.3</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>1126922-621-CM26</t>
+          <t>1336-77-CM26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -22964,17 +22960,17 @@
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -22999,13 +22995,13 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>3847.3</v>
+        <v>1846.7</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>1336-77-CM26</t>
+          <t>3481-65-CM26</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -23025,17 +23021,17 @@
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>61.101.015-K</t>
         </is>
       </c>
       <c r="G361" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H361" t="inlineStr">
@@ -23045,22 +23041,26 @@
       </c>
       <c r="I361" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J361" t="inlineStr">
         <is>
-          <t>77.203.369-9</t>
-        </is>
-      </c>
-      <c r="K361" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>1846.7</v>
+        <v>1168.35</v>
       </c>
     </row>
     <row r="362">
@@ -23192,7 +23192,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>1116005-45-CM26</t>
+          <t>2852-448-CM26</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -23217,12 +23217,12 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H364" t="inlineStr">
@@ -23232,12 +23232,12 @@
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>SEGURYCEL SA</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>99.510.910-7</t>
         </is>
       </c>
       <c r="K364" t="inlineStr"/>
@@ -23247,13 +23247,13 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>923.87</v>
+        <v>1838.47</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>2852-448-CM26</t>
+          <t>2297-659-CM26</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -23273,17 +23273,17 @@
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H365" t="inlineStr">
@@ -23293,12 +23293,12 @@
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>SEGURYCEL SA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
         <is>
-          <t>99.510.910-7</t>
+          <t>77.676.860-k</t>
         </is>
       </c>
       <c r="K365" t="inlineStr"/>
@@ -23308,13 +23308,13 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>1838.47</v>
+        <v>8833.52</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>2297-659-CM26</t>
+          <t>1116005-45-CM26</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -23334,17 +23334,17 @@
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
@@ -23354,12 +23354,12 @@
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K366" t="inlineStr"/>
@@ -23369,13 +23369,13 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>8833.52</v>
+        <v>923.87</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>2297-677-CM26</t>
+          <t>2297-678-CM26</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -23415,12 +23415,12 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>COMERCIAL JOAQUIN LIMITADA</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>76.288.097-0</t>
         </is>
       </c>
       <c r="K367" t="inlineStr"/>
@@ -23430,13 +23430,13 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>6349.47</v>
+        <v>4256.04</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>2297-678-CM26</t>
+          <t>2297-677-CM26</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>COMERCIAL JOAQUIN LIMITADA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
         <is>
-          <t>76.288.097-0</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K368" t="inlineStr"/>
@@ -23491,7 +23491,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>4256.04</v>
+        <v>6349.47</v>
       </c>
     </row>
     <row r="369">
@@ -23558,7 +23558,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>2852-489-CM26</t>
+          <t>437-39-CM26</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -23578,17 +23578,17 @@
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G370" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H370" t="inlineStr">
@@ -23598,28 +23598,32 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J370" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K370" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>975.52</v>
+        <v>1241.25</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>437-39-CM26</t>
+          <t>1057532-814-CM26</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -23639,17 +23643,17 @@
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.607.600-0</t>
         </is>
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SERVICIO DE SALUD OSORNO</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -23659,12 +23663,12 @@
       </c>
       <c r="I371" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>BIKE RED MACHINE SPA</t>
         </is>
       </c>
       <c r="J371" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>76.856.309-8</t>
         </is>
       </c>
       <c r="K371" t="inlineStr">
@@ -23678,13 +23682,13 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>1241.25</v>
+        <v>7776.21</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>1057532-814-CM26</t>
+          <t>2852-489-CM26</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -23709,12 +23713,12 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>61.607.600-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23724,26 +23728,22 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>BIKE RED MACHINE SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J372" t="inlineStr">
         <is>
-          <t>76.856.309-8</t>
-        </is>
-      </c>
-      <c r="K372" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr"/>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>7776.21</v>
+        <v>975.52</v>
       </c>
     </row>
     <row r="373">
@@ -23810,7 +23810,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>2852-501-CM26</t>
+          <t>2297-712-CM26</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -23830,17 +23830,17 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G374" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H374" t="inlineStr">
@@ -23850,17 +23850,17 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J374" t="inlineStr">
         <is>
-          <t>77.537.871-9</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K374" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L374" t="inlineStr">
@@ -23869,13 +23869,13 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>22849.26</v>
+        <v>4062.97</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>2297-712-CM26</t>
+          <t>2852-501-CM26</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -23895,17 +23895,17 @@
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23915,17 +23915,17 @@
       </c>
       <c r="I375" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD DE INVERSIONES DASSEN SPA</t>
         </is>
       </c>
       <c r="J375" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.537.871-9</t>
         </is>
       </c>
       <c r="K375" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L375" t="inlineStr">
@@ -23934,7 +23934,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>4062.97</v>
+        <v>22849.26</v>
       </c>
     </row>
     <row r="376">
@@ -24070,7 +24070,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>387-348-CM26</t>
+          <t>387-347-CM26</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -24110,32 +24110,28 @@
       </c>
       <c r="I378" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
         </is>
       </c>
       <c r="J378" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K378" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.397.758-7</t>
+        </is>
+      </c>
+      <c r="K378" t="inlineStr"/>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>6505.28</v>
+        <v>863.42</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>387-347-CM26</t>
+          <t>387-348-CM26</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -24175,22 +24171,26 @@
       </c>
       <c r="I379" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS VIALES LIMITADA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J379" t="inlineStr">
         <is>
-          <t>76.397.758-7</t>
-        </is>
-      </c>
-      <c r="K379" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>863.42</v>
+        <v>6505.28</v>
       </c>
     </row>
     <row r="380">
@@ -24578,7 +24578,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>2328-688-CM26</t>
+          <t>2328-687-CM26</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -24618,17 +24618,17 @@
       </c>
       <c r="I386" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J386" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K386" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L386" t="inlineStr">
@@ -24637,13 +24637,13 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>27492.4</v>
+        <v>18644.44</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>2328-689-CM26</t>
+          <t>2328-688-CM26</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -24683,17 +24683,17 @@
       </c>
       <c r="I387" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J387" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
+          <t>77.454.264-7</t>
         </is>
       </c>
       <c r="K387" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="L387" t="inlineStr">
@@ -24702,13 +24702,13 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>7762.61</v>
+        <v>27492.4</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>2328-687-CM26</t>
+          <t>2328-689-CM26</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -24767,7 +24767,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>18644.44</v>
+        <v>7762.61</v>
       </c>
     </row>
     <row r="389">
@@ -24838,7 +24838,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>2297-786-CM26</t>
+          <t>2324-833-CM26</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -24858,17 +24858,17 @@
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H390" t="inlineStr">
@@ -24878,12 +24878,12 @@
       </c>
       <c r="I390" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J390" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K390" t="inlineStr"/>
@@ -24893,7 +24893,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>1639.32</v>
+        <v>813.97</v>
       </c>
     </row>
     <row r="391">
@@ -24964,7 +24964,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>5413-586-CM26</t>
+          <t>2297-786-CM26</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -24989,12 +24989,12 @@
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>70.772.100-6</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G392" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LOS LAGOS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H392" t="inlineStr">
@@ -25019,13 +25019,13 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>855.66</v>
+        <v>1639.32</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>2324-833-CM26</t>
+          <t>1173430-89-CM26</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -25050,12 +25050,12 @@
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.950.500-K</t>
         </is>
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -25065,22 +25065,26 @@
       </c>
       <c r="I393" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J393" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
-        </is>
-      </c>
-      <c r="K393" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>813.97</v>
+        <v>2088.66</v>
       </c>
     </row>
     <row r="394">
@@ -25151,7 +25155,7 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>1173430-89-CM26</t>
+          <t>5413-586-CM26</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -25171,17 +25175,17 @@
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>61.950.500-K</t>
+          <t>70.772.100-6</t>
         </is>
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>UNIVERSIDAD DE LOS LAGOS</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -25191,26 +25195,22 @@
       </c>
       <c r="I395" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J395" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K395" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr"/>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2088.66</v>
+        <v>855.66</v>
       </c>
     </row>
     <row r="396">
@@ -25655,7 +25655,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>2289-590-CM26</t>
+          <t>2297-867-CM26</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -25680,12 +25680,12 @@
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>69.220.700-9</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
@@ -25695,32 +25695,28 @@
       </c>
       <c r="I403" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J403" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K403" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K403" t="inlineStr"/>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>2789.88</v>
+        <v>4074.53</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>2297-867-CM26</t>
+          <t>2289-590-CM26</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -25745,12 +25741,12 @@
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.700-9</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -25760,22 +25756,26 @@
       </c>
       <c r="I404" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J404" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K404" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>4074.53</v>
+        <v>2789.88</v>
       </c>
     </row>
     <row r="405">
@@ -25976,7 +25976,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>2297-883-CM26</t>
+          <t>796290-57-CM26</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -25996,17 +25996,17 @@
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>61.103.006-1</t>
         </is>
       </c>
       <c r="G408" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H408" t="inlineStr">
@@ -26016,28 +26016,32 @@
       </c>
       <c r="I408" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J408" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K408" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>3500.94</v>
+        <v>3807.86</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>796290-57-CM26</t>
+          <t>2297-883-CM26</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -26057,17 +26061,17 @@
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>61.103.006-1</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
@@ -26077,26 +26081,22 @@
       </c>
       <c r="I409" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J409" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K409" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K409" t="inlineStr"/>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>3807.86</v>
+        <v>3500.94</v>
       </c>
     </row>
     <row r="410">
@@ -26362,7 +26362,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1126922-912-CM26</t>
+          <t>2328-846-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -26382,17 +26382,17 @@
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
@@ -26402,28 +26402,32 @@
       </c>
       <c r="I414" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J414" t="inlineStr">
         <is>
-          <t>77.203.369-9</t>
-        </is>
-      </c>
-      <c r="K414" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>7925.11</v>
+        <v>24832.11</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>2328-846-CM26</t>
+          <t>1126922-912-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -26443,17 +26447,17 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -26463,26 +26467,22 @@
       </c>
       <c r="I415" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
         </is>
       </c>
       <c r="J415" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K415" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.203.369-9</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr"/>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>24832.11</v>
+        <v>7925.11</v>
       </c>
     </row>
     <row r="416">
@@ -26553,7 +26553,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1894-236-CM26</t>
+          <t>1126922-922-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -26578,12 +26578,12 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -26593,32 +26593,28 @@
       </c>
       <c r="I417" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
         </is>
       </c>
       <c r="J417" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K417" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.231.391-K</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr"/>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>33713.91</v>
+        <v>22613.13</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>1126922-922-CM26</t>
+          <t>1894-236-CM26</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -26643,12 +26639,12 @@
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -26658,22 +26654,26 @@
       </c>
       <c r="I418" t="inlineStr">
         <is>
-          <t>EMPRESA COMERCIALIZADORA LUIS VALDES LYON SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J418" t="inlineStr">
         <is>
-          <t>76.231.391-K</t>
-        </is>
-      </c>
-      <c r="K418" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>22613.13</v>
+        <v>33713.91</v>
       </c>
     </row>
     <row r="419">
@@ -27829,7 +27829,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>1810-36-CM26</t>
+          <t>1393093-721-CM26</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -27854,12 +27854,12 @@
       </c>
       <c r="F437" t="inlineStr">
         <is>
-          <t>60.703.000-6</t>
+          <t>61.981.360-K</t>
         </is>
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -27869,28 +27869,32 @@
       </c>
       <c r="I437" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J437" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
-        </is>
-      </c>
-      <c r="K437" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>816.08</v>
+        <v>52564.13</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>1393093-721-CM26</t>
+          <t>1810-36-CM26</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -27915,12 +27919,12 @@
       </c>
       <c r="F438" t="inlineStr">
         <is>
-          <t>61.981.360-K</t>
+          <t>60.703.000-6</t>
         </is>
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DE CHILOÉ</t>
+          <t>INSTITUTO NACIONAL DE ESTADISTICAS</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -27930,26 +27934,22 @@
       </c>
       <c r="I438" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J438" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K438" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K438" t="inlineStr"/>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>52564.13</v>
+        <v>816.08</v>
       </c>
     </row>
     <row r="439">
@@ -28077,7 +28077,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>2324-1155-CM26</t>
+          <t>1002-387-CM26</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -28097,17 +28097,17 @@
       </c>
       <c r="E441" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F441" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -28117,32 +28117,28 @@
       </c>
       <c r="I441" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J441" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K441" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.961.103-7</t>
+        </is>
+      </c>
+      <c r="K441" t="inlineStr"/>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>15005.63</v>
+        <v>26926.91</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>1037-89-CM26</t>
+          <t>3289-116-CM26</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -28162,17 +28158,17 @@
       </c>
       <c r="E442" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F442" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G442" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H442" t="inlineStr">
@@ -28182,12 +28178,12 @@
       </c>
       <c r="I442" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>COMERCIAL CM EXPRESS LIMITADA</t>
         </is>
       </c>
       <c r="J442" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
+          <t>76.579.703-9</t>
         </is>
       </c>
       <c r="K442" t="inlineStr"/>
@@ -28197,13 +28193,13 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>3780.1</v>
+        <v>985.21</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>1002-387-CM26</t>
+          <t>2324-1155-CM26</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -28223,17 +28219,17 @@
       </c>
       <c r="E443" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F443" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -28243,28 +28239,32 @@
       </c>
       <c r="I443" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J443" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
-        </is>
-      </c>
-      <c r="K443" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>26926.91</v>
+        <v>15005.63</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>3289-116-CM26</t>
+          <t>1037-89-CM26</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -28284,17 +28284,17 @@
       </c>
       <c r="E444" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F444" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -28304,12 +28304,12 @@
       </c>
       <c r="I444" t="inlineStr">
         <is>
-          <t>COMERCIAL CM EXPRESS LIMITADA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J444" t="inlineStr">
         <is>
-          <t>76.579.703-9</t>
+          <t>76.691.662-7</t>
         </is>
       </c>
       <c r="K444" t="inlineStr"/>
@@ -28319,13 +28319,13 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>985.21</v>
+        <v>3780.1</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>2852-855-CM26</t>
+          <t>1002-392-CM26</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -28350,12 +28350,12 @@
       </c>
       <c r="F445" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G445" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H445" t="inlineStr">
@@ -28365,12 +28365,12 @@
       </c>
       <c r="I445" t="inlineStr">
         <is>
-          <t>ELECTROCOM S A</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
         </is>
       </c>
       <c r="J445" t="inlineStr">
         <is>
-          <t>96.355.000-6</t>
+          <t>76.961.103-7</t>
         </is>
       </c>
       <c r="K445" t="inlineStr"/>
@@ -28380,7 +28380,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>1776.58</v>
+        <v>10508.41</v>
       </c>
     </row>
     <row r="446">
@@ -28447,7 +28447,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>1002-392-CM26</t>
+          <t>2852-855-CM26</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -28472,12 +28472,12 @@
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -28487,12 +28487,12 @@
       </c>
       <c r="I447" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS Y SERVICIOS  PROCOMERCE SPA</t>
+          <t>ELECTROCOM S A</t>
         </is>
       </c>
       <c r="J447" t="inlineStr">
         <is>
-          <t>76.961.103-7</t>
+          <t>96.355.000-6</t>
         </is>
       </c>
       <c r="K447" t="inlineStr"/>
@@ -28502,13 +28502,13 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>10508.41</v>
+        <v>1776.58</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>707425-159-CM26</t>
+          <t>707425-156-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -28528,7 +28528,7 @@
       </c>
       <c r="E448" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F448" t="inlineStr">
@@ -28548,32 +28548,28 @@
       </c>
       <c r="I448" t="inlineStr">
         <is>
-          <t>BIKE RED MACHINE SPA</t>
+          <t>MARYUN Seguridad Industrial</t>
         </is>
       </c>
       <c r="J448" t="inlineStr">
         <is>
-          <t>76.856.309-8</t>
-        </is>
-      </c>
-      <c r="K448" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.084.730-3</t>
+        </is>
+      </c>
+      <c r="K448" t="inlineStr"/>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>18919.15</v>
+        <v>13381.33</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>707425-156-CM26</t>
+          <t>707425-159-CM26</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -28593,7 +28589,7 @@
       </c>
       <c r="E449" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F449" t="inlineStr">
@@ -28613,28 +28609,32 @@
       </c>
       <c r="I449" t="inlineStr">
         <is>
-          <t>MARYUN Seguridad Industrial</t>
+          <t>BIKE RED MACHINE SPA</t>
         </is>
       </c>
       <c r="J449" t="inlineStr">
         <is>
-          <t>77.084.730-3</t>
-        </is>
-      </c>
-      <c r="K449" t="inlineStr"/>
+          <t>76.856.309-8</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>13381.33</v>
+        <v>18919.15</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>3289-123-CM26</t>
+          <t>1173430-142-CM26</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -28659,12 +28659,12 @@
       </c>
       <c r="F450" t="inlineStr">
         <is>
-          <t>60.506.000-5</t>
+          <t>61.950.500-K</t>
         </is>
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -28674,28 +28674,32 @@
       </c>
       <c r="I450" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J450" t="inlineStr">
         <is>
-          <t>77.203.369-9</t>
-        </is>
-      </c>
-      <c r="K450" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>877.7</v>
+        <v>1832.74</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>1173430-142-CM26</t>
+          <t>3289-123-CM26</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -28720,12 +28724,12 @@
       </c>
       <c r="F451" t="inlineStr">
         <is>
-          <t>61.950.500-K</t>
+          <t>60.506.000-5</t>
         </is>
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -28735,32 +28739,28 @@
       </c>
       <c r="I451" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
         </is>
       </c>
       <c r="J451" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K451" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.203.369-9</t>
+        </is>
+      </c>
+      <c r="K451" t="inlineStr"/>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>1832.74</v>
+        <v>877.7</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>2854-1067-CM26</t>
+          <t>2306-756-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -28785,12 +28785,12 @@
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>69.220.200-7</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
@@ -28819,13 +28819,13 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>5647.49</v>
+        <v>4314.06</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2306-756-CM26</t>
+          <t>2854-1067-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -28850,12 +28850,12 @@
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.220.200-7</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE PUERTO VARAS</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
@@ -28884,13 +28884,13 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>4314.06</v>
+        <v>5647.49</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>2297-1143-CM26</t>
+          <t>707425-167-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -28910,17 +28910,17 @@
       </c>
       <c r="E454" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -28930,32 +28930,28 @@
       </c>
       <c r="I454" t="inlineStr">
         <is>
-          <t>DAT I GES SPA</t>
+          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
         </is>
       </c>
       <c r="J454" t="inlineStr">
         <is>
-          <t>77.328.681-7</t>
-        </is>
-      </c>
-      <c r="K454" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.691.662-7</t>
+        </is>
+      </c>
+      <c r="K454" t="inlineStr"/>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>9480.219999999999</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>707425-167-CM26</t>
+          <t>2297-1143-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -28975,17 +28971,17 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
@@ -28995,22 +28991,26 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA EMPORIO DEL ABUELO LUCIANO ARRAÑO E.I.R.L.</t>
+          <t>DAT I GES SPA</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>76.691.662-7</t>
-        </is>
-      </c>
-      <c r="K455" t="inlineStr"/>
+          <t>77.328.681-7</t>
+        </is>
+      </c>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2125</v>
+        <v>9480.219999999999</v>
       </c>
     </row>
     <row r="456">
@@ -29593,7 +29593,7 @@
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>162-392-CM26</t>
+          <t>1095-66-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -29613,17 +29613,17 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
@@ -29633,28 +29633,32 @@
       </c>
       <c r="I465" t="inlineStr">
         <is>
-          <t>RAC SEGURIDAD INDUSTRIAL</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J465" t="inlineStr">
         <is>
-          <t>77.676.860-k</t>
-        </is>
-      </c>
-      <c r="K465" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>2949.37</v>
+        <v>1009.3</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>3507-651-CM26</t>
+          <t>162-392-CM26</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -29674,17 +29678,17 @@
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>65.321.890-7</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CALBUCO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H466" t="inlineStr">
@@ -29694,32 +29698,28 @@
       </c>
       <c r="I466" t="inlineStr">
         <is>
-          <t>COMERCIAL GRAN VIA SPA</t>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
         </is>
       </c>
       <c r="J466" t="inlineStr">
         <is>
-          <t>77.831.858-K</t>
-        </is>
-      </c>
-      <c r="K466" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K466" t="inlineStr"/>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>3592.78</v>
+        <v>2949.37</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>1126922-1383-CM26</t>
+          <t>3507-651-CM26</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -29739,17 +29739,17 @@
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>65.321.890-7</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
@@ -29778,13 +29778,13 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>889.21</v>
+        <v>3592.78</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>1095-66-CM26</t>
+          <t>1126922-1383-CM26</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -29804,17 +29804,17 @@
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -29824,17 +29824,17 @@
       </c>
       <c r="I468" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>COMERCIAL GRAN VIA SPA</t>
         </is>
       </c>
       <c r="J468" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
+          <t>77.831.858-K</t>
         </is>
       </c>
       <c r="K468" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L468" t="inlineStr">
@@ -29843,7 +29843,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>1009.3</v>
+        <v>889.21</v>
       </c>
     </row>
     <row r="469">
@@ -31048,7 +31048,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>1126922-1519-CM26</t>
+          <t>1173430-198-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -31068,17 +31068,17 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>61.950.500-K</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
@@ -31088,28 +31088,32 @@
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>77.203.369-9</t>
-        </is>
-      </c>
-      <c r="K488" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>3773.67</v>
+        <v>901.9</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>1173430-198-CM26</t>
+          <t>1126922-1519-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -31134,12 +31138,12 @@
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>61.950.500-K</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
@@ -31149,32 +31153,28 @@
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K489" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.203.369-9</t>
+        </is>
+      </c>
+      <c r="K489" t="inlineStr"/>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>901.9</v>
+        <v>3773.67</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>3443-802-CM26</t>
+          <t>1860-88-CM26</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -31199,12 +31199,12 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>69.210.500-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PURRANQUE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
@@ -31214,12 +31214,12 @@
       </c>
       <c r="I490" t="inlineStr">
         <is>
-          <t>SHERWIN WILLIAMS CHILE S A</t>
+          <t>Lars Christian</t>
         </is>
       </c>
       <c r="J490" t="inlineStr">
         <is>
-          <t>96.803.460-k</t>
+          <t>78.725.520-5</t>
         </is>
       </c>
       <c r="K490" t="inlineStr"/>
@@ -31229,13 +31229,13 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>1891.49</v>
+        <v>942.99</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>1860-88-CM26</t>
+          <t>3443-802-CM26</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -31260,12 +31260,12 @@
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.210.500-1</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE PURRANQUE</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
@@ -31275,12 +31275,12 @@
       </c>
       <c r="I491" t="inlineStr">
         <is>
-          <t>Lars Christian</t>
+          <t>SHERWIN WILLIAMS CHILE S A</t>
         </is>
       </c>
       <c r="J491" t="inlineStr">
         <is>
-          <t>78.725.520-5</t>
+          <t>96.803.460-k</t>
         </is>
       </c>
       <c r="K491" t="inlineStr"/>
@@ -31290,7 +31290,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>942.99</v>
+        <v>1891.49</v>
       </c>
     </row>
     <row r="492">
@@ -31446,7 +31446,7 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
@@ -31617,7 +31617,7 @@
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>1126922-1567-CM26</t>
+          <t>2328-1463-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -31642,12 +31642,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -31657,28 +31657,32 @@
       </c>
       <c r="I497" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
+          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
         </is>
       </c>
       <c r="J497" t="inlineStr">
         <is>
-          <t>77.203.369-9</t>
-        </is>
-      </c>
-      <c r="K497" t="inlineStr"/>
+          <t>77.454.264-7</t>
+        </is>
+      </c>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>897.4</v>
+        <v>35695</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>2328-1463-CM26</t>
+          <t>2328-1465-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -31737,13 +31741,13 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>35695</v>
+        <v>68945.14999999999</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>2328-1465-CM26</t>
+          <t>1126922-1567-CM26</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -31768,12 +31772,12 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -31783,26 +31787,83 @@
       </c>
       <c r="I499" t="inlineStr">
         <is>
-          <t>DISTRIBUIDORA E IMPORTADORA DE MATERIALES DE FERRETERIA Y CONSTRUCCION DEL SUR SPA</t>
+          <t>SOCIEDAD COMERCIAL Y DE SERVICIOS LIBERTAD SPA</t>
         </is>
       </c>
       <c r="J499" t="inlineStr">
         <is>
-          <t>77.454.264-7</t>
-        </is>
-      </c>
-      <c r="K499" t="inlineStr">
-        <is>
-          <t>Araucanía</t>
-        </is>
-      </c>
+          <t>77.203.369-9</t>
+        </is>
+      </c>
+      <c r="K499" t="inlineStr"/>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>68945.14999999999</v>
+        <v>897.4</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>1301-97-CM26</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>2239-9-LR23</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>61.313.000-4</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>CORP NACIONAL FORESTAL</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>RAC SEGURIDAD INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="J500" t="inlineStr">
+        <is>
+          <t>77.676.860-k</t>
+        </is>
+      </c>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M500" s="2" t="n">
+        <v>1296.82</v>
       </c>
     </row>
   </sheetData>
